--- a/data/trans_bre/P2A_fisi_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 2,67</t>
+          <t>-2,53; 2,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 4,98</t>
+          <t>-2,34; 4,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 4,11</t>
+          <t>-2,28; 3,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 0,02</t>
+          <t>-6,52; -0,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,78; 133,73</t>
+          <t>-56,83; 124,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,54; 158,1</t>
+          <t>-40,48; 140,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,91; 179,04</t>
+          <t>-44,01; 155,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-58,68; 2,03</t>
+          <t>-56,66; 0,65</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,57</t>
+          <t>-1,26; 4,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 4,2</t>
+          <t>-2,92; 4,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 1,51</t>
+          <t>-4,21; 1,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 2,5</t>
+          <t>-3,95; 2,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,05; 313,88</t>
+          <t>-37,12; 310,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,37; 106,11</t>
+          <t>-41,91; 114,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-68,17; 56,42</t>
+          <t>-71,11; 49,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,87; 44,14</t>
+          <t>-44,06; 51,31</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 7,52</t>
+          <t>-1,86; 7,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 4,71</t>
+          <t>-3,79; 5,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 8,16</t>
+          <t>-3,05; 7,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 13,97</t>
+          <t>-2,01; 14,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,8; 157,15</t>
+          <t>-28,19; 156,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 68,07</t>
+          <t>-39,71; 83,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-39,98; 159,78</t>
+          <t>-40,21; 147,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 341,44</t>
+          <t>-18,41; 374,01</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,76</t>
+          <t>-2,13; 2,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 3,3</t>
+          <t>-2,08; 3,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 2,8</t>
+          <t>-1,68; 3,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 51,9</t>
+          <t>-4,44; 44,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 48,71</t>
+          <t>-29,78; 52,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,42; 41,03</t>
+          <t>-20,56; 40,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,53; 52,57</t>
+          <t>-24,78; 58,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,06; 468,93</t>
+          <t>-34,62; 400,63</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,71</t>
+          <t>-2,18; 4,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 7,67</t>
+          <t>1,2; 7,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 5,27</t>
+          <t>-0,32; 5,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,2; -0,52</t>
+          <t>-10,15; -0,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,66; 111,51</t>
+          <t>-26,54; 113,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,88; 148,77</t>
+          <t>9,37; 136,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 123,88</t>
+          <t>-7,27; 125,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-46,11; -3,87</t>
+          <t>-48,62; -1,3</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,37</t>
+          <t>2,02; 6,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 7,36</t>
+          <t>0,61; 7,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 5,83</t>
+          <t>-0,26; 5,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,97; 14,05</t>
+          <t>5,48; 14,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,3; 726,87</t>
+          <t>48,34; 795,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,76; 282,56</t>
+          <t>6,15; 297,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 197,66</t>
+          <t>-5,7; 171,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49,9; 648,64</t>
+          <t>49,09; 600,51</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,51</t>
+          <t>0,15; 2,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,09</t>
+          <t>0,42; 3,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,57</t>
+          <t>0,14; 2,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 20,81</t>
+          <t>-0,35; 21,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 56,4</t>
+          <t>2,66; 54,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,17; 46,44</t>
+          <t>5,74; 46,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 51,2</t>
+          <t>1,89; 50,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 210,66</t>
+          <t>-3,3; 197,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_fisi_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,13</t>
+          <t>-2,73</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-34,74%</t>
+          <t>-31,68%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,74</t>
+          <t>-2,56; 2,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 4,98</t>
+          <t>-2,64; 5,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,92</t>
+          <t>-1,83; 4,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,52; -0,11</t>
+          <t>-5,64; 0,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-56,83; 124,37</t>
+          <t>-58,77; 147,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,48; 140,87</t>
+          <t>-45,13; 173,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-44,01; 155,04</t>
+          <t>-41,26; 171,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-56,66; 0,65</t>
+          <t>-54,14; 11,25</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-7,96%</t>
+          <t>-5,15%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,47</t>
+          <t>-1,09; 4,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 4,25</t>
+          <t>-2,96; 4,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 1,45</t>
+          <t>-4,18; 1,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 2,5</t>
+          <t>-3,61; 2,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,12; 310,27</t>
+          <t>-35,16; 305,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 114,09</t>
+          <t>-43,84; 116,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,11; 49,13</t>
+          <t>-72,33; 54,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,06; 51,31</t>
+          <t>-41,37; 51,96</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>-1,32%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 7,48</t>
+          <t>-1,89; 7,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 5,69</t>
+          <t>-3,52; 5,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 7,64</t>
+          <t>-2,58; 7,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 14,68</t>
+          <t>-4,88; 5,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,19; 156,63</t>
+          <t>-28,27; 140,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,71; 83,3</t>
+          <t>-35,88; 77,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-40,21; 147,31</t>
+          <t>-36,55; 143,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,41; 374,01</t>
+          <t>-36,15; 60,36</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,64</t>
+          <t>-3,05</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>126,5%</t>
+          <t>-24,89%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,87</t>
+          <t>-1,69; 3,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 3,26</t>
+          <t>-2,3; 3,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 3,06</t>
+          <t>-1,69; 3,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 44,68</t>
+          <t>-5,68; -0,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,78; 52,06</t>
+          <t>-24,12; 57,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 40,46</t>
+          <t>-22,6; 43,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 58,14</t>
+          <t>-22,37; 61,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 400,63</t>
+          <t>-41,29; -6,49</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-4,32</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-24,97%</t>
+          <t>-0,24%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,62</t>
+          <t>-2,78; 4,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,67</t>
+          <t>1,08; 7,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 5,18</t>
+          <t>-0,34; 5,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -0,14</t>
+          <t>-3,81; 3,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 113,03</t>
+          <t>-31,58; 93,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,37; 136,19</t>
+          <t>12,14; 140,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 125,57</t>
+          <t>-6,51; 120,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-48,62; -1,3</t>
+          <t>-21,31; 27,97</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,47</t>
+          <t>10,01</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>209,75%</t>
+          <t>198,83%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,47</t>
+          <t>1,94; 6,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 7,41</t>
+          <t>0,96; 7,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 5,67</t>
+          <t>-0,29; 5,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 14,02</t>
+          <t>4,64; 13,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48,34; 795,1</t>
+          <t>43,2; 680,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,15; 297,32</t>
+          <t>10,47; 305,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 171,56</t>
+          <t>-4,9; 214,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49,09; 600,51</t>
+          <t>37,04; 531,21</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,41</t>
+          <t>0,11; 2,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,05</t>
+          <t>0,51; 3,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,48</t>
+          <t>0,07; 2,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 21,1</t>
+          <t>-1,11; 1,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 54,11</t>
+          <t>2,4; 54,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,74; 46,65</t>
+          <t>6,68; 50,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 50,81</t>
+          <t>0,9; 50,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 197,01</t>
+          <t>-9,42; 17,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_fisi_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
